--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484606_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484606_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9897</v>
+        <v>4.1399</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3356</v>
+        <v>3.006</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6541</v>
+        <v>1.1338</v>
       </c>
       <c r="G2" t="n">
         <v>3.025</v>
@@ -610,13 +610,13 @@
         <v>3.1154</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2474</v>
+        <v>0.3976</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0407</v>
+        <v>-0.3702</v>
       </c>
       <c r="U2" t="n">
-        <v>1.2881</v>
+        <v>0.7679</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1679</v>
+        <v>1.0857</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3342</v>
+        <v>0.252</v>
       </c>
       <c r="F4" t="n">
         <v>0.8337</v>
@@ -766,10 +766,10 @@
         <v>2.3823</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.184</v>
+        <v>-0.2662</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3333</v>
+        <v>-0.4155</v>
       </c>
       <c r="U4" t="n">
         <v>0.1493</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8472</v>
+        <v>0.8938</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5681</v>
+        <v>0.6642</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2792</v>
+        <v>0.2296</v>
       </c>
       <c r="G5" t="n">
         <v>-0.7351</v>
@@ -844,13 +844,13 @@
         <v>1.0995</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4727</v>
+        <v>-0.4261</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5151</v>
+        <v>-0.4189</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0424</v>
+        <v>-0.0072</v>
       </c>
       <c r="V5" t="n">
         <v>0.9554</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1928</v>
+        <v>0.74</v>
       </c>
       <c r="E6" t="n">
-        <v>0.274</v>
+        <v>0.6726</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.08119999999999999</v>
+        <v>0.0675</v>
       </c>
       <c r="G6" t="n">
         <v>-1.5207</v>
@@ -922,13 +922,13 @@
         <v>2.3823</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.0012</v>
+        <v>-0.454</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.5758</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0269</v>
+        <v>0.1218</v>
       </c>
       <c r="V6" t="n">
         <v>0.3324</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1408</v>
+        <v>-0.7315</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9301</v>
+        <v>-1.5454</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7892</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="G7" t="n">
         <v>-1.7984</v>
@@ -1000,13 +1000,13 @@
         <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0755</v>
+        <v>0.3339</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.092</v>
+        <v>0.2926</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0165</v>
+        <v>0.0413</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. ARNAU BELTRAN</t>
+          <t>R. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.1164</v>
+        <v>-2.5408</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0851</v>
+        <v>-3.4684</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0313</v>
+        <v>0.9276</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.4841</v>
+        <v>-2.9877</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9647</v>
+        <v>-0.8181</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.4488</v>
+        <v>-2.1696</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.5512</v>
+        <v>-2.7618</v>
       </c>
       <c r="K8" t="n">
-        <v>1.5448</v>
+        <v>-0.2075</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.096</v>
+        <v>-2.5543</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9329</v>
+        <v>-0.2259</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5800999999999999</v>
+        <v>-0.6106</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3528</v>
+        <v>0.3846</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8326</v>
+        <v>1.4661</v>
       </c>
       <c r="S8" t="n">
-        <v>1.3623</v>
+        <v>0.2191</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1154</v>
+        <v>0.2097</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2469</v>
+        <v>0.0094</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9109</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
-        <v>1.267</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.1778</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HOLGADO CUELLAR</t>
+          <t>P. ARNAU BELTRAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2774</v>
+        <v>-2.7374</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.1555</v>
+        <v>-0.607</v>
       </c>
       <c r="F9" t="n">
-        <v>0.878</v>
+        <v>-2.1304</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.9877</v>
+        <v>-2.4841</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8181</v>
+        <v>0.9647</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1696</v>
+        <v>-3.4488</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.7618</v>
+        <v>-1.5512</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.2075</v>
+        <v>1.5448</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.5543</v>
+        <v>-3.096</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2259</v>
+        <v>-0.9329</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6106</v>
+        <v>-0.5800999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3846</v>
+        <v>-0.3528</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5498</v>
+        <v>0.9163</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4661</v>
+        <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5175</v>
+        <v>0.7413</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4774</v>
+        <v>0.5935</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0401</v>
+        <v>0.1478</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3219</v>
+        <v>-1.9109</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.267</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.3219</v>
+        <v>-3.1778</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3799</v>
+        <v>-3.4513</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6343</v>
+        <v>-3.7304</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2544</v>
+        <v>0.2791</v>
       </c>
       <c r="G10" t="n">
         <v>-5.0601</v>
@@ -1234,13 +1234,13 @@
         <v>2.0158</v>
       </c>
       <c r="S10" t="n">
-        <v>0.9313</v>
+        <v>0.8599</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6395</v>
+        <v>0.5434</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2918</v>
+        <v>0.3165</v>
       </c>
       <c r="V10" t="n">
         <v>-1.267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4443</v>
+        <v>-5.0093</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.6005</v>
+        <v>-1.5865</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.8439</v>
+        <v>-3.4227</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7123</v>
@@ -1312,13 +1312,13 @@
         <v>2.3823</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.2976</v>
+        <v>-0.8625</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6267</v>
+        <v>-0.6127</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.671</v>
+        <v>-0.2498</v>
       </c>
       <c r="V11" t="n">
         <v>-1.9005</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.960700000000002</v>
+        <v>-5.410399999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.693099999999999</v>
+        <v>-4.1424</v>
       </c>
       <c r="F12" t="n">
         <v>-1.2678</v>
@@ -1390,10 +1390,10 @@
         <v>17.4093</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.00749999999999984</v>
+        <v>0.5429999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.3046</v>
+        <v>-0.7539000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>1.297</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4396</v>
+        <v>4.0404</v>
       </c>
       <c r="E13" t="n">
-        <v>5.0366</v>
+        <v>4.4596</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.597</v>
+        <v>-0.4193</v>
       </c>
       <c r="G13" t="n">
         <v>2.8387</v>
@@ -1468,13 +1468,13 @@
         <v>1.0995</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7842</v>
+        <v>0.385</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5113</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2728</v>
+        <v>0.4506</v>
       </c>
       <c r="V13" t="n">
         <v>0.6335</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9091</v>
+        <v>3.5631</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1969</v>
+        <v>1.9661</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7122</v>
+        <v>1.5971</v>
       </c>
       <c r="G14" t="n">
         <v>3.7044</v>
@@ -1546,13 +1546,13 @@
         <v>0.9163</v>
       </c>
       <c r="S14" t="n">
-        <v>0.121</v>
+        <v>0.7751</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0098</v>
+        <v>-0.2405</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1308</v>
+        <v>1.0156</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>J. MONTILLA GONZALEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2559</v>
+        <v>1.5578</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.6143</v>
+        <v>1.52</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8702</v>
+        <v>0.0378</v>
       </c>
       <c r="G15" t="n">
-        <v>3.7025</v>
+        <v>3.3709</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0129</v>
+        <v>1.7847</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7154</v>
+        <v>1.5862</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7854</v>
+        <v>3.6264</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8328</v>
+        <v>3.418</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9526</v>
+        <v>0.2084</v>
       </c>
       <c r="M15" t="n">
-        <v>0.917</v>
+        <v>-0.2555</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8457</v>
+        <v>-1.6333</v>
       </c>
       <c r="O15" t="n">
-        <v>1.7628</v>
+        <v>1.3778</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.9321</v>
+        <v>-2.7489</v>
       </c>
       <c r="Q15" t="n">
         <v>-3.6651</v>
       </c>
       <c r="R15" t="n">
-        <v>0.733</v>
+        <v>0.9163</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1636</v>
+        <v>0.6139</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0565</v>
+        <v>-0.0301</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2201</v>
+        <v>0.644</v>
       </c>
       <c r="V15" t="n">
         <v>0.3219</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3219</v>
+        <v>1.5889</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. CORNEJO GONZALEZ</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0424</v>
+        <v>1.4089</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.179</v>
+        <v>-0.6143</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2214</v>
+        <v>2.0232</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0838</v>
+        <v>3.7025</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7623</v>
+        <v>-0.0129</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8461</v>
+        <v>3.7154</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4927</v>
+        <v>2.7854</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.576</v>
+        <v>0.8328</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0833</v>
+        <v>1.9526</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5765</v>
+        <v>0.917</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1863</v>
+        <v>-0.8457</v>
       </c>
       <c r="O16" t="n">
         <v>1.7628</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3665</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9163</v>
+        <v>-3.6651</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3084</v>
+        <v>0.3165</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.092</v>
+        <v>-0.0565</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2164</v>
+        <v>0.3731</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6335</v>
+        <v>0.3219</v>
       </c>
       <c r="W16" t="n">
         <v>0.3219</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MONTILLA GONZALEZ</t>
+          <t>M. CORNEJO GONZALEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8001</v>
+        <v>1.1138</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7123</v>
+        <v>-1.0828</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9122</v>
+        <v>2.1966</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3709</v>
+        <v>1.0838</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7847</v>
+        <v>-0.7623</v>
       </c>
       <c r="I17" t="n">
-        <v>1.5862</v>
+        <v>1.8461</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6264</v>
+        <v>-0.4927</v>
       </c>
       <c r="K17" t="n">
-        <v>3.418</v>
+        <v>-0.576</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2084</v>
+        <v>0.0833</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2555</v>
+        <v>1.5765</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6333</v>
+        <v>-0.1863</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3778</v>
+        <v>1.7628</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7489</v>
+        <v>-0.3665</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.6651</v>
+        <v>-0.9163</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9163</v>
+        <v>0.5498</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1439</v>
+        <v>-0.237</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1622</v>
+        <v>0.0042</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3061</v>
+        <v>-0.2412</v>
       </c>
       <c r="V17" t="n">
+        <v>0.6335</v>
+      </c>
+      <c r="W17" t="n">
         <v>0.3219</v>
       </c>
-      <c r="W17" t="n">
-        <v>1.5889</v>
-      </c>
       <c r="X17" t="n">
-        <v>-1.267</v>
+        <v>0.3115</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. FOS CERVERA</t>
+          <t>D. GONZALEZ FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7524999999999999</v>
+        <v>0.3351</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3603</v>
+        <v>-0.0977</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3922</v>
+        <v>0.4328</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1892</v>
+        <v>0.4901</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.1635</v>
+        <v>-0.9555</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0258</v>
+        <v>1.4456</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2793</v>
+        <v>0.0674</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1951</v>
+        <v>-0.641</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.4743</v>
+        <v>0.7085</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.91</v>
+        <v>0.4226</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3585</v>
+        <v>-0.3145</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4486</v>
+        <v>0.7371</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3665</v>
+        <v>0.5498</v>
       </c>
       <c r="S18" t="n">
-        <v>1.5856</v>
+        <v>-0.7048</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6395</v>
+        <v>-0.1652</v>
       </c>
       <c r="U18" t="n">
-        <v>0.946</v>
+        <v>-0.5396</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.0104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. GONZALEZ FERRER</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2855</v>
+        <v>0.0499</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0977</v>
+        <v>0.518</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3832</v>
+        <v>-0.4681</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4901</v>
+        <v>1.4428</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9555</v>
+        <v>0.2024</v>
       </c>
       <c r="I19" t="n">
-        <v>1.4456</v>
+        <v>1.2404</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0674</v>
+        <v>2.3698</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.641</v>
+        <v>1.6098</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7085</v>
+        <v>0.76</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4226</v>
+        <v>-0.927</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3145</v>
+        <v>-1.4074</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7371</v>
+        <v>0.4804</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5498</v>
+        <v>-2.9321</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.6651</v>
       </c>
       <c r="R19" t="n">
-        <v>0.5498</v>
+        <v>0.733</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7543</v>
+        <v>-0.3612</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1652</v>
+        <v>-0.4091</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5891</v>
+        <v>0.0479</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.9005</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.2224</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>B. FOS CERVERA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6145</v>
+        <v>-0.2922</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2295</v>
+        <v>-0.3128</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.844</v>
+        <v>0.0206</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4428</v>
+        <v>-1.1892</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2024</v>
+        <v>-1.1635</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2404</v>
+        <v>-0.0258</v>
       </c>
       <c r="J20" t="n">
-        <v>2.3698</v>
+        <v>-0.2793</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6098</v>
+        <v>0.1951</v>
       </c>
       <c r="L20" t="n">
-        <v>0.76</v>
+        <v>-0.4743</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.927</v>
+        <v>-0.91</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4074</v>
+        <v>-1.3585</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4804</v>
+        <v>0.4486</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.9321</v>
+        <v>0.3665</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6651</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.733</v>
+        <v>0.3665</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0256</v>
+        <v>0.5409</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6976</v>
+        <v>-0.0335</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3281</v>
+        <v>0.5744</v>
       </c>
       <c r="V20" t="n">
-        <v>1.9005</v>
+        <v>-0.0104</v>
       </c>
       <c r="W20" t="n">
-        <v>2.2224</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.3219</v>
+        <v>-0.0104</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.7336</v>
+        <v>-0.9464</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5938</v>
+        <v>0.4015</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3275</v>
+        <v>-1.3479</v>
       </c>
       <c r="G21" t="n">
         <v>-0.2846</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6347</v>
+        <v>0.4219</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2187</v>
+        <v>0.0264</v>
       </c>
       <c r="U21" t="n">
-        <v>0.416</v>
+        <v>0.3955</v>
       </c>
       <c r="V21" t="n">
         <v>-1.267</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9089</v>
+        <v>-1.7895</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0242</v>
+        <v>-3.7357</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1153</v>
+        <v>1.9462</v>
       </c>
       <c r="G22" t="n">
         <v>0.3865</v>
@@ -2170,13 +2170,13 @@
         <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3242</v>
+        <v>-0.2048</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6976</v>
+        <v>-0.4091</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3734</v>
+        <v>0.2043</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3219</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2672</v>
+        <v>-1.798</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9465</v>
+        <v>-1.7542</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3207</v>
+        <v>-0.0438</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7252</v>
@@ -2248,13 +2248,13 @@
         <v>0.1833</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7252</v>
+        <v>-0.256</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1101</v>
+        <v>0.0822</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6151</v>
+        <v>-0.3382</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>5.960900000000001</v>
+        <v>7.242899999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>1.2677</v>
+        <v>1.267700000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>4.693099999999999</v>
+        <v>5.9752</v>
       </c>
       <c r="G24" t="n">
         <v>13.8207</v>
@@ -2302,13 +2302,13 @@
         <v>12.9848</v>
       </c>
       <c r="K24" t="n">
-        <v>8.014400000000002</v>
+        <v>8.0144</v>
       </c>
       <c r="L24" t="n">
-        <v>4.9706</v>
+        <v>4.970600000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8356999999999998</v>
+        <v>0.8356999999999997</v>
       </c>
       <c r="N24" t="n">
         <v>-9.739100000000001</v>
@@ -2323,22 +2323,22 @@
         <v>-17.4094</v>
       </c>
       <c r="R24" t="n">
-        <v>7.3303</v>
+        <v>7.330299999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>0.007499999999999951</v>
+        <v>1.2895</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2971</v>
+        <v>-1.2968</v>
       </c>
       <c r="U24" t="n">
-        <v>1.3043</v>
+        <v>2.586400000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>2.212000000000001</v>
+        <v>2.212</v>
       </c>
       <c r="W24" t="n">
-        <v>6.989000000000001</v>
+        <v>6.989</v>
       </c>
       <c r="X24" t="n">
         <v>-4.7772</v>
